--- a/data/trans_dic/IP19C08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor</t>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 14,66</t>
+          <t>1,7; 15,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 17,27</t>
+          <t>3,18; 17,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,96</t>
+          <t>1,39; 11,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>0,0; 16,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,68</t>
+          <t>3,25; 12,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,88</t>
+          <t>0,67; 5,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,29</t>
+          <t>3,14; 7,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,95</t>
+          <t>3,09; 8,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,59</t>
+          <t>2,96; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,35</t>
+          <t>0,97; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,6</t>
+          <t>3,12; 7,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,26</t>
+          <t>1,99; 5,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,84</t>
+          <t>1,7; 5,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,24</t>
+          <t>0,83; 7,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,05</t>
+          <t>3,81; 7,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,2</t>
+          <t>2,99; 6,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,78</t>
+          <t>2,81; 5,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,14</t>
+          <t>1,34; 5,26</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 13,68</t>
+          <t>2,84; 12,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,93</t>
+          <t>1,54; 8,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,54</t>
+          <t>0,57; 5,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,11</t>
+          <t>0,84; 6,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,35</t>
+          <t>0,89; 8,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,83</t>
+          <t>2,37; 9,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,11</t>
+          <t>2,3; 8,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,16</t>
+          <t>1,72; 6,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,0</t>
+          <t>0,67; 4,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,38</t>
+          <t>2,2; 7,0</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,89</t>
+          <t>3,97; 8,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,28</t>
+          <t>2,81; 6,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,76</t>
+          <t>2,39; 5,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,83</t>
+          <t>1,16; 3,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,93</t>
+          <t>3,29; 6,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,51</t>
+          <t>2,42; 5,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,47</t>
+          <t>1,44; 4,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,51</t>
+          <t>1,87; 6,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,79</t>
+          <t>4,06; 7,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,25</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,37</t>
+          <t>2,28; 4,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,61</t>
+          <t>1,88; 4,56</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3055</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3510</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6565</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>798; 7171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1365; 7689</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>599; 5081</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4304</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2922; 11485</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>607; 5232</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3957</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11863</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11431</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12064</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8286</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8696</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24463</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20389</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20350</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14803</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7177; 17963</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6804; 18225</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7471; 18608</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2545; 11499</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7661; 19090</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4796; 14246</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4280; 13821</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2669; 25037</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>18053; 33962</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13806; 28579</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14155; 29958</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7819; 30744</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2913</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6480</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6395</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9099</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2150; 9710</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7631</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>500; 4495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>845; 6151</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4109</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>727; 6674</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4338</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3222; 12768</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3416; 12317</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2887; 11209</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1175; 7094</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5183; 16518</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14912</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13833</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>37508</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28703</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23546</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>25037</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13941; 28110</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9961; 22226</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8671; 21266</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4549; 13992</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11913; 25213</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8871; 20132</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5302; 15297</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9080; 32013</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>28943; 50166</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>20456; 37950</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>16612; 31921</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>16461; 39989</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Estudios-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 15,28</t>
+          <t>1,68; 15,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 17,93</t>
+          <t>3,15; 17,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,83</t>
+          <t>1,35; 12,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,89</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,79</t>
+          <t>3,76; 12,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,75</t>
+          <t>0,66; 6,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,87</t>
+          <t>3,21; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,27</t>
+          <t>3,31; 8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,36</t>
+          <t>2,96; 7,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,39</t>
+          <t>1,12; 4,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,77</t>
+          <t>3,29; 7,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,91</t>
+          <t>1,99; 6,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,5</t>
+          <t>1,89; 5,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,75</t>
+          <t>0,91; 7,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,16</t>
+          <t>3,67; 6,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,19</t>
+          <t>2,82; 6,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,94</t>
+          <t>2,81; 5,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,26</t>
+          <t>1,3; 5,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 12,83</t>
+          <t>3,06; 13,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,92</t>
+          <t>1,55; 8,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,12</t>
+          <t>0,57; 5,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,15</t>
+          <t>0,87; 5,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,13</t>
+          <t>0,9; 7,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,39</t>
+          <t>2,31; 9,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,28</t>
+          <t>2,09; 7,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,69</t>
+          <t>1,77; 6,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,04</t>
+          <t>0,67; 3,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,0</t>
+          <t>2,17; 6,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,01</t>
+          <t>3,98; 7,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,28</t>
+          <t>2,58; 6,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,86</t>
+          <t>2,38; 5,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,57</t>
+          <t>1,24; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,97</t>
+          <t>3,13; 6,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,5</t>
+          <t>2,25; 5,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,17</t>
+          <t>1,44; 4,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,61</t>
+          <t>1,96; 6,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,04</t>
+          <t>4,03; 6,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>2,85; 5,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,37</t>
+          <t>2,24; 4,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,56</t>
+          <t>1,86; 4,54</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>798; 7171</t>
+          <t>790; 7350</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1365; 7689</t>
+          <t>1352; 7320</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>599; 5081</t>
+          <t>580; 5212</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1539,17 +1539,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4304</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2922; 11485</t>
+          <t>3374; 11566</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607; 5232</t>
+          <t>601; 5613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3957</t>
+          <t>0; 4249</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7177; 17963</t>
+          <t>7329; 18528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6804; 18225</t>
+          <t>7288; 17680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7471; 18608</t>
+          <t>7489; 18652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2545; 11499</t>
+          <t>2927; 11613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7661; 19090</t>
+          <t>8096; 19344</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4796; 14246</t>
+          <t>4794; 14464</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4280; 13821</t>
+          <t>4759; 14954</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2669; 25037</t>
+          <t>2954; 25105</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18053; 33962</t>
+          <t>17403; 32144</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13806; 28579</t>
+          <t>13025; 27952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14155; 29958</t>
+          <t>14163; 28402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7819; 30744</t>
+          <t>7617; 30447</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2150; 9710</t>
+          <t>2316; 9868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1320; 7631</t>
+          <t>1323; 7218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>500; 4495</t>
+          <t>497; 5006</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>845; 6151</t>
+          <t>874; 5861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>727; 6674</t>
+          <t>737; 6474</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>0; 4743</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3222; 12768</t>
+          <t>3144; 13482</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3416; 12317</t>
+          <t>3114; 11567</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2887; 11209</t>
+          <t>2969; 11098</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1175; 7094</t>
+          <t>1168; 6753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5183; 16518</t>
+          <t>5127; 16218</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13941; 28110</t>
+          <t>13968; 27982</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9961; 22226</t>
+          <t>9148; 21767</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8671; 21266</t>
+          <t>8625; 21034</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4549; 13992</t>
+          <t>4838; 14905</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11913; 25213</t>
+          <t>11336; 24622</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8871; 20132</t>
+          <t>8242; 20937</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5302; 15297</t>
+          <t>5292; 15409</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9080; 32013</t>
+          <t>9516; 32833</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28943; 50166</t>
+          <t>28707; 48048</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20456; 37950</t>
+          <t>20538; 38228</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16612; 31921</t>
+          <t>16379; 31571</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16461; 39989</t>
+          <t>16252; 39753</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -717,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,66</t>
+          <t>3,12; 17,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1,4; 12,96</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 14,81</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,48; 14,66</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,15; 17,07</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 12,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,76</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,88</t>
+          <t>3,21; 12,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,17</t>
+          <t>0,67; 5,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>0,0; 7,46</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,77%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,11</t>
+          <t>3,27; 7,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,02</t>
+          <t>1,98; 6,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,38</t>
+          <t>1,87; 5,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,44</t>
+          <t>0,9; 8,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,87</t>
+          <t>3,29; 8,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,0</t>
+          <t>3,06; 7,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,95</t>
+          <t>2,79; 7,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,77</t>
+          <t>0,94; 4,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,78</t>
+          <t>3,74; 7,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,06</t>
+          <t>3,1; 6,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,63</t>
+          <t>2,71; 5,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,21</t>
+          <t>1,27; 5,33</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 13,04</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,44</t>
+          <t>0,89; 9,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,71</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,86</t>
+          <t>2,38; 9,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>2,87; 13,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,88</t>
+          <t>1,52; 8,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,56; 5,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,92</t>
+          <t>0,89; 5,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,77</t>
+          <t>2,32; 8,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,62</t>
+          <t>1,84; 7,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,85</t>
+          <t>0,41; 4,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,87</t>
+          <t>1,85; 6,13</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,97</t>
+          <t>3,21; 6,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,15</t>
+          <t>2,39; 5,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,8</t>
+          <t>1,57; 4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,81</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,81</t>
+          <t>4,08; 7,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,72</t>
+          <t>2,54; 6,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,2</t>
+          <t>2,39; 5,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,78</t>
+          <t>1,12; 3,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,74</t>
+          <t>4,05; 6,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,31</t>
+          <t>2,9; 5,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,33</t>
+          <t>2,19; 4,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,54</t>
+          <t>1,92; 4,7</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,62 +1436,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3510</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3055</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6565</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>1919</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6565</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>986</t>
         </is>
       </c>
     </row>
@@ -1504,52 +1504,52 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>790; 7350</t>
+          <t>1336; 7409</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>602; 5569</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3597</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>695; 6880</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1352; 7320</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>580; 5212</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4016</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3374; 11566</t>
+          <t>2879; 11392</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>601; 5613</t>
+          <t>611; 5343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4249</t>
+          <t>0; 3802</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8286</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8628</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11863</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11431</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>12064</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8958</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8286</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14786</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7329; 18528</t>
+          <t>8032; 18678</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7288; 17680</t>
+          <t>4774; 15088</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7489; 18652</t>
+          <t>4706; 14678</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2927; 11613</t>
+          <t>2786; 27457</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8096; 19344</t>
+          <t>7509; 18927</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4794; 14464</t>
+          <t>6740; 17531</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4759; 14954</t>
+          <t>7050; 19194</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2954; 25105</t>
+          <t>2502; 11811</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17403; 32144</t>
+          <t>17721; 33414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13025; 27952</t>
+          <t>14309; 28623</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14163; 28402</t>
+          <t>13680; 29115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7617; 30447</t>
+          <t>7296; 30679</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2913</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3481</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1769</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2561</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2913</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8381</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2316; 9868</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1323; 7218</t>
+          <t>727; 7683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497; 5006</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>874; 5861</t>
+          <t>3027; 12019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4231</t>
+          <t>2173; 10353</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>737; 6474</t>
+          <t>1305; 7643</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4743</t>
+          <t>493; 4863</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3144; 13482</t>
+          <t>922; 6201</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3114; 11567</t>
+          <t>3447; 12073</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2969; 11098</t>
+          <t>3092; 12004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1168; 6753</t>
+          <t>714; 7015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5127; 16218</t>
+          <t>4267; 14159</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13968; 27982</t>
+          <t>11614; 25056</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9148; 21767</t>
+          <t>8733; 20159</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8625; 21034</t>
+          <t>5763; 16416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4838; 14905</t>
+          <t>8342; 30526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11336; 24622</t>
+          <t>14335; 27686</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8242; 20937</t>
+          <t>8974; 22241</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5292; 15409</t>
+          <t>8650; 20898</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9516; 32833</t>
+          <t>4428; 15038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28707; 48048</t>
+          <t>28877; 48374</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20538; 38228</t>
+          <t>20870; 37795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16379; 31571</t>
+          <t>16009; 31894</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16252; 39753</t>
+          <t>16501; 40308</t>
         </is>
       </c>
     </row>
